--- a/Automation_practice/amazon_cart_items.xlsx
+++ b/Automation_practice/amazon_cart_items.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A17"/>
+  <dimension ref="A1:A18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,112 +438,119 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Xiaomi 14 (White, 12GB RAM, 512GB Storage) | 50MP Leica Professional Optics | 120 Hz 1.5K LTPO AMOLED | SD 8 Gen 3 Hyper OS</t>
+          <t>Apple iPhone 15 Pro (128 GB) - Natural Titanium</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Vivo V30 5G (Peacock Green, 256GB Storage) (8GB RAM)</t>
+          <t>Apple iPhone 14 (128 GB) - Blue</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Apple iPhone 14 (128 GB) - Purple</t>
+          <t>Apple iPhone 15 (512 GB) - Blue</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Apple iPhone 15 Pro (128 GB) - White Titanium</t>
+          <t>Apple iPhone 15 Plus (128 GB) - Pink</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Apple iPhone 13 (256GB) - Pink</t>
+          <t>Apple iPhone 15 Plus (128 GB) - Green</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Apple iPhone 14 (128 GB) - Blue</t>
+          <t>Apple iPhone 15 (256 GB) - Pink</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Apple iPhone 15 Pro (128 GB) - Natural Titanium</t>
+          <t>Apple iPhone 15 Plus (128 GB) - Black</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Apple iPhone 15 Plus (128 GB) - Green</t>
+          <t>Apple iPhone 15 Plus (128 GB) - Blue</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Apple iPhone 14 Plus (512 GB) - Blue</t>
+          <t>Apple iPhone 15 (256 GB) - Black</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Apple iPhone 13 (128GB) - Blue</t>
+          <t>Apple iPhone 15 (128 GB) - Yellow</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Apple iPhone 15 Plus (128 GB) - Black</t>
+          <t>Apple iPhone 15 (256 GB) - Blue</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Apple iPhone 15 (128 GB) - Green</t>
+          <t>Apple iPhone 15 (256 GB) - Green</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Apple iPhone 15 (128 GB) - Pink</t>
+          <t>Apple iPhone 15 (128 GB) - Green</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Apple iPhone 15 (128 GB) - Black</t>
+          <t>Apple iPhone 15 (128 GB) - Pink</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Apple iPhone 15 (128 GB) - Blue</t>
+          <t>Apple iPhone 15 (128 GB) - Black</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Apple iPhone 14 (128 GB) - Midnight</t>
+          <t>Apple iPhone 15 (128 GB) - Blue</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Apple iPhone 15 Plus (256 GB) - Blue</t>
         </is>
       </c>
     </row>
